--- a/attached_assets/reports/KONTi_Dashboard_Feedback_Consolidated_v4.xlsx
+++ b/attached_assets/reports/KONTi_Dashboard_Feedback_Consolidated_v4.xlsx
@@ -937,7 +937,7 @@
     <t>Fase 5 operates under the Cost-Plus model, which includes a management fee component. Fee transparency in the client report is a V1 billing requirement.</t>
   </si>
   <si>
-    <t>EN: Management Fee row on the project report now shows a "?" tooltip with the calculation formula and an inline Edit → link to /calculator?tab=contractor. | ES: La fila de Honorarios de Administración en el reporte ahora muestra un tooltip "?" con la fórmula de cálculo y un enlace Editar → en línea a /calculator?tab=contractor.</t>
+    <t>EN: Management Fee row on the project report now shows a "?" tooltip with the calculation formula and an inline Edit → link to /calculator?tab=overview (calculator aliases this to the Contractor tab where the fee % field lives). | ES: La fila de Honorarios de Administración en el reporte ahora muestra un tooltip "?" con la fórmula y un enlace Editar → en línea a /calculator?tab=overview (la calculadora redirige este alias a la pestaña Contratista donde se edita el % de honorarios).</t>
   </si>
   <si>
     <t>C-08</t>
@@ -1054,7 +1054,7 @@
     <t>Minor CSS fix on an existing V1 report page. No new scope required.</t>
   </si>
   <si>
-    <t>EN: Light theme background flipped from #F4F2EE off-white to pure #FFFFFF white for cleaner client-facing PDFs. | ES: El fondo del tema Claro cambió de #F4F2EE a blanco puro #FFFFFF para PDFs más limpios al cliente.</t>
+    <t>EN: Added a "White background" preset (3rd state) to the report theme cycle alongside Light and Dark; selection persists per project (konti.report.theme.&lt;projectId&gt;) and survives reload. | ES: Se agregó un preset "Fondo Blanco" (tercer estado) al ciclo de temas del reporte junto con Claro y Oscuro; la selección se guarda por proyecto (konti.report.theme.&lt;projectId&gt;) y persiste al recargar.</t>
   </si>
   <si>
     <t xml:space="preserve">  AI Assistant</t>

--- a/attached_assets/reports/KONTi_Dashboard_Feedback_Consolidated_v4.xlsx
+++ b/attached_assets/reports/KONTi_Dashboard_Feedback_Consolidated_v4.xlsx
@@ -451,7 +451,7 @@
     <t>Fase 3 includes 'Herramientas de estimación de costos' and 'Envío de comparación real vs. estimado'. The cost calculator with CSV import is a core V1 estimation tool.</t>
   </si>
   <si>
-    <t>EN: Calculator landing now opens with the Estimating tab as default and remembers last-used tab via localStorage. | ES: La calculadora abre por defecto en la pestaña Estimación y recuerda la última pestaña usada vía localStorage.</t>
+    <t>EN: CSV importer now uses smart EN/ES column mapping with override dropdowns, 5-row preview, skipped-row panel, and per-project mapping memory in localStorage (Task #112). Files: artifacts/konti-dashboard/src/components/estimating/imports-panel.tsx + e2e/csv-mapping-import.spec.ts. | ES: El importador CSV ahora usa mapeo inteligente de columnas EN/ES con menús de sobrescritura, vista previa de 5 filas, panel de filas omitidas, y memoria de mapeo por proyecto en localStorage (Tarea #112). Archivos: artifacts/konti-dashboard/src/components/estimating/imports-panel.tsx + e2e/csv-mapping-import.spec.ts.</t>
   </si>
   <si>
     <t>B-02</t>
@@ -595,7 +595,7 @@
     <t>Label clarity in the cost calculator is a V1 UX requirement. This is a minor copy/tooltip fix that supports accurate estimate presentation.</t>
   </si>
   <si>
-    <t>EN: Imports tab renamed to "Imported Materials" with explainer banner clarifying imports merge into Materials/Labor/Receipts buckets, not a separate cost category. | ES: Pestaña renombrada a "Materiales Importados" con banner explicativo que aclara que los imports se fusionan en los baldes de Materiales/Mano de Obra/Recibos, no son una categoría aparte.</t>
+    <t>EN: Imports tab renamed to "Imported Materials" with explainer banner (data-testid="imports-explainer") clarifying that imports merge into the Materials/Labor/Receipts buckets, not a separate cost category. File: artifacts/konti-dashboard/src/components/estimating/imports-panel.tsx. | ES: Pestaña renombrada a "Materiales Importados" con banner explicativo (data-testid="imports-explainer") que aclara que los imports se fusionan en los baldes de Materiales/Mano de Obra/Recibos, no son una categoría aparte. Archivo: artifacts/konti-dashboard/src/components/estimating/imports-panel.tsx.</t>
   </si>
   <si>
     <t>B-08</t>
@@ -619,7 +619,7 @@
     <t>Minor UX polish on an existing V1 calculator field. No new feature scope required.</t>
   </si>
   <si>
-    <t>EN: "?" tooltip on labor baseline panel + Effective Price tooltip on calculator explain how the effective hourly rate is computed (3 most-recent receipts ÷ hours, or last CSV import). | ES: Tooltip "?" en el panel de línea base de mano de obra + tooltip Precio Efectivo en la calculadora explican cómo se calcula la tarifa efectiva por hora (3 recibos más recientes ÷ horas, o último CSV).</t>
+    <t>EN: Keyboard-focusable "?" button on the labor-baseline panel (data-testid="effective-rate-tooltip") + Effective Price tooltip on calculator explain how the effective hourly rate is computed (3 most-recent receipts ÷ hours, or last CSV import). File: artifacts/konti-dashboard/src/components/estimating/imports-panel.tsx + pages/calculator.tsx. | ES: Botón "?" enfocable por teclado en el panel de línea base de mano de obra (data-testid="effective-rate-tooltip") + tooltip Precio Efectivo en la calculadora explican cómo se calcula la tarifa efectiva por hora (3 recibos más recientes ÷ horas, o último CSV). Archivo: artifacts/konti-dashboard/src/components/estimating/imports-panel.tsx + pages/calculator.tsx.</t>
   </si>
   <si>
     <t>B-09</t>
@@ -643,7 +643,7 @@
     <t>Fase 3 includes 'Envío de comparación real vs. estimado'. The receipts/variance tab is a core V1 feature; improving its discoverability is a V1 navigation fix.</t>
   </si>
   <si>
-    <t>EN: Variance Snapshot card on the project detail page deep-links to /calculator?projectId=…&amp;tab=variance for one-click drill-down. | ES: Tarjeta Resumen de Variación en la página de proyecto enlaza directo a /calculator?projectId=…&amp;tab=variance para acceso de un clic.</t>
+    <t>EN: Variance Snapshot card on project-detail (data-testid="variance-snapshot-link") deep-links to /calculator?projectId=…&amp;tab=variance for one-click drill-down from the project page. File: artifacts/konti-dashboard/src/pages/project-detail.tsx. | ES: Tarjeta Resumen de Variación en project-detail (data-testid="variance-snapshot-link") enlaza directo a /calculator?projectId=…&amp;tab=variance para acceso de un clic desde la página del proyecto. Archivo: artifacts/konti-dashboard/src/pages/project-detail.tsx.</t>
   </si>
   <si>
     <t>B-10</t>
@@ -673,7 +673,7 @@
     <t>Data persistence is a fundamental V1 infrastructure requirement. This is a critical bug fix, not a new feature.</t>
   </si>
   <si>
-    <t>EN: Calculator now persists last-used tab and filters per project in localStorage; reopening a project restores the previous view. | ES: La calculadora guarda la última pestaña y filtros usados por proyecto en localStorage; al reabrir un proyecto se restaura la vista anterior.</t>
+    <t>EN: Receipts persistence — PROJECT_RECEIPTS and PROJECT_REPORT_TEMPLATE now hydrate from loadJSON on boot and persist via saveJSON on every change, so receipts survive an api-server restart. Files: artifacts/api-server/src/routes/projects.ts + storage snapshot layer. | ES: Persistencia de recibos — PROJECT_RECEIPTS y PROJECT_REPORT_TEMPLATE ahora cargan desde loadJSON al iniciar y se guardan vía saveJSON en cada cambio, sobreviviendo a un reinicio del api-server. Archivos: artifacts/api-server/src/routes/projects.ts + capa de snapshot.</t>
   </si>
   <si>
     <t>B-11</t>
@@ -721,7 +721,7 @@
     <t>Fase 3 includes client-facing PDF presentations (Presentaciones V1-V4). Branded PDF export from the calculator is a core V1 deliverable.</t>
   </si>
   <si>
-    <t>EN: Bid summary now exports XLSX with the same columns as the on-screen view, plus brand header and totals row. | ES: El resumen de licitación ahora exporta XLSX con las mismas columnas que la vista en pantalla, más encabezado de marca y fila de totales.</t>
+    <t>EN: PDF report uses saved template — renderTemplateCostReport now consumes PROJECT_REPORT_TEMPLATE[project.id] so the templated columns/header/footer drive the export instead of hard-coded defaults. File: artifacts/api-server/src/routes/projects.ts. | ES: El reporte PDF usa la plantilla guardada — renderTemplateCostReport ahora consume PROJECT_REPORT_TEMPLATE[project.id] así que las columnas/encabezado/pie de la plantilla guían la exportación en lugar de valores fijos. Archivo: artifacts/api-server/src/routes/projects.ts.</t>
   </si>
   <si>
     <t>B-13</t>
@@ -796,7 +796,7 @@
     <t>Fase 5 explicitly lists punchlist items and contractor monitoring as client deliverables. A complete punchlist in the report is a core V1 construction-phase requirement.</t>
   </si>
   <si>
-    <t>EN: Partial — punchlist entries support photo attachments (multi-file upload, lightbox preview), but the per-project photo-link rollup on the report page is still pending. | ES: Parcial — las entradas de punchlist permiten adjuntar fotos (carga múltiple, vista lightbox), pero el resumen de enlaces de fotos por proyecto en el reporte aún está pendiente.</t>
+    <t>EN: Partial — PunchlistPanel and ContractorMonitoringSection are now mounted inside project-report.tsx so the client report shows live punchlist + contractor monitoring data. Photo-link rollup (per-project gallery of all punchlist photos) is still pending — covered by follow-up #115. | ES: Parcial — PunchlistPanel y ContractorMonitoringSection están ahora montados en project-report.tsx, así el reporte del cliente muestra datos en vivo de punchlist y monitoreo de contratista. El resumen de enlaces de fotos por proyecto sigue pendiente — cubierto por la tarea de seguimiento #115.</t>
   </si>
   <si>
     <t>C-02</t>
@@ -889,7 +889,7 @@
     <t>Minor label fix on an existing V1 report field. No new scope required.</t>
   </si>
   <si>
-    <t>EN: Weather card on the project report uses the label "Weather Status" (was "Weather Risk") in both Key Metrics and the dedicated weather panel. | ES: La tarjeta de clima en el reporte usa la etiqueta "Estado del Clima" (antes "Riesgo Climático") tanto en Métricas Clave como en el panel dedicado.</t>
+    <t>EN: Weather card on the project report uses the label "Weather Status" (was "Weather Risk") in both Key Metrics and the dedicated weather panel. File: artifacts/konti-dashboard/src/pages/project-report.tsx. | ES: La tarjeta de clima en el reporte usa la etiqueta "Estado del Clima" (antes "Riesgo Climático") tanto en Métricas Clave como en el panel dedicado. Archivo: artifacts/konti-dashboard/src/pages/project-report.tsx.</t>
   </si>
   <si>
     <t>C-06</t>
@@ -937,7 +937,7 @@
     <t>Fase 5 operates under the Cost-Plus model, which includes a management fee component. Fee transparency in the client report is a V1 billing requirement.</t>
   </si>
   <si>
-    <t>EN: Management Fee row on the project report now shows a "?" tooltip with the calculation formula and an inline Edit → link to /calculator?tab=overview (calculator aliases this to the Contractor tab where the fee % field lives). | ES: La fila de Honorarios de Administración en el reporte ahora muestra un tooltip "?" con la fórmula y un enlace Editar → en línea a /calculator?tab=overview (la calculadora redirige este alias a la pestaña Contratista donde se edita el % de honorarios).</t>
+    <t>EN: Management Fee row on the project report now shows a focusable "?" tooltip with the calculation formula and an inline Edit → link to /calculator?tab=overview (calculator aliases overview→contractor so the user lands on the editable field). File: artifacts/konti-dashboard/src/pages/project-report.tsx + pages/calculator.tsx. | ES: La fila de Honorarios de Administración en el reporte ahora muestra un tooltip "?" enfocable con la fórmula y un enlace Editar → en línea a /calculator?tab=overview (la calculadora redirige overview→contractor para que el usuario llegue al campo editable). Archivo: artifacts/konti-dashboard/src/pages/project-report.tsx + pages/calculator.tsx.</t>
   </si>
   <si>
     <t>C-08</t>
@@ -961,7 +961,7 @@
     <t>Brand consistency on client-facing reports is a V1 baseline requirement. This is a trivial CSS fix.</t>
   </si>
   <si>
-    <t>EN: Report header logo bumped from h-14/16/20 to h-20/24/28 (~80/96/112 px) so it reads clearly on print and at the top of PDF exports. | ES: El logo del encabezado del reporte aumentó de h-14/16/20 a h-20/24/28 (~80/96/112 px) para verse claramente al imprimir y en exportaciones PDF.</t>
+    <t>EN: Report header logo bumped from h-14/16/20 to h-20/24/28 (~80/96/112 px) so it reads clearly on print and at the top of PDF exports. File: artifacts/konti-dashboard/src/pages/project-report.tsx. | ES: El logo del encabezado del reporte aumentó de h-14/16/20 a h-20/24/28 (~80/96/112 px) para verse claramente al imprimir y en exportaciones PDF. Archivo: artifacts/konti-dashboard/src/pages/project-report.tsx.</t>
   </si>
   <si>
     <t>C-09</t>
@@ -1030,7 +1030,7 @@
     <t>Fase 5 lists 'inspecciones, reportes, de avance' as client deliverables. Site photos are a core part of construction progress reporting in V1.</t>
   </si>
   <si>
-    <t>EN: Project report exposes a Light/Dark/Sepia theme toggle persisted in localStorage; Light is the default. | ES: El reporte de proyecto incluye un selector de tema Claro/Oscuro/Sepia guardado en localStorage; Claro es el predeterminado.</t>
+    <t>EN: Site photos in report — site-photos-gallery component is rendered on the project report and PHOTO_CATEGORY_OPTIONS is wired into the report's photos block so each photo carries a category label. File: artifacts/konti-dashboard/src/pages/project-report.tsx + components/site-photos-gallery.tsx. | ES: Fotos de obra en el reporte — el componente site-photos-gallery se muestra en el reporte del proyecto y PHOTO_CATEGORY_OPTIONS está conectado al bloque de fotos del reporte para que cada foto tenga etiqueta de categoría. Archivo: artifacts/konti-dashboard/src/pages/project-report.tsx + components/site-photos-gallery.tsx.</t>
   </si>
   <si>
     <t>C-12</t>
@@ -1054,7 +1054,7 @@
     <t>Minor CSS fix on an existing V1 report page. No new scope required.</t>
   </si>
   <si>
-    <t>EN: Added a "White background" preset (3rd state) to the report theme cycle alongside Light and Dark; selection persists per project (konti.report.theme.&lt;projectId&gt;) and survives reload. | ES: Se agregó un preset "Fondo Blanco" (tercer estado) al ciclo de temas del reporte junto con Claro y Oscuro; la selección se guarda por proyecto (konti.report.theme.&lt;projectId&gt;) y persiste al recargar.</t>
+    <t>EN: Added a "White background" preset (3rd state) to the report theme cycle (light → white → dark → light); legacy light preset retains sand-tinted #F4F2EE while the new white preset is pure #FFFFFF. Selection persists per project (konti.report.theme.&lt;projectId&gt;) and survives reload. File: artifacts/konti-dashboard/src/pages/project-report.tsx. | ES: Se agregó un preset "Fondo Blanco" (tercer estado) al ciclo de temas del reporte (claro → blanco → oscuro → claro); el preset claro original mantiene su tono arena #F4F2EE mientras el nuevo preset blanco es #FFFFFF puro. La selección se guarda por proyecto (konti.report.theme.&lt;projectId&gt;) y persiste al recargar. Archivo: artifacts/konti-dashboard/src/pages/project-report.tsx.</t>
   </si>
   <si>
     <t xml:space="preserve">  AI Assistant</t>
@@ -1081,7 +1081,7 @@
     <t>The V1 workflow does not include an AI assistant module. The AI assistant is not referenced in any of the 5 workflow phases. This entire feature is out of V1 scope; persistence is moot until the feature itself is scoped for V2.</t>
   </si>
   <si>
-    <t>EN: Demo dataset (demo@konti.com) seeded with 6 projects, contractor estimates, receipts, punchlist items, weather snapshots and labor rates so the dashboard is populated on first login. | ES: Conjunto de datos demo (demo@konti.com) con 6 proyectos, estimados de contratista, recibos, punchlist, snapshots de clima y tarifas de mano de obra para que el dashboard se vea completo al primer ingreso.</t>
+    <t>EN: AI assistant persistence — PROJECT_NOTES and SPEC_EVENTS now use the same loadJSON/saveJSON snapshot, so notes and AI spec events survive a server restart. Files: artifacts/api-server/src/routes/* + storage layer. | ES: Persistencia del asistente IA — PROJECT_NOTES y SPEC_EVENTS ahora usan el mismo snapshot loadJSON/saveJSON, sobreviviendo a un reinicio del servidor. Archivos: artifacts/api-server/src/routes/* + capa de almacenamiento.</t>
   </si>
   <si>
     <t>D-02</t>
@@ -1402,7 +1402,7 @@
     <t>Data persistence is a fundamental V1 infrastructure requirement. This is a critical bug fix affecting all modules across all workflow phases.</t>
   </si>
   <si>
-    <t>EN: Partial — document upload UI works (drag-drop, type detection, project linking) but blob storage is still in-memory; persistent App Storage migration is the remaining piece. | ES: Parcial — la UI de carga de documentos funciona (drag-drop, detección de tipo, enlace a proyecto) pero el almacenamiento de blobs aún es en memoria; la migración a App Storage persistente es lo pendiente.</t>
+    <t>EN: Partial — demo-project upload persistence: notes, punchlist and receipts now persist across server restarts (#B-10/D-01/I-03), but document blob storage is still in-memory. Follow-up #114 will migrate doc blobs to App Storage to fully close I-01. | ES: Parcial — persistencia de cargas del proyecto demo: notas, punchlist y recibos ya persisten entre reinicios (#B-10/D-01/I-03), pero el almacenamiento de blobs de documentos sigue en memoria. La tarea de seguimiento #114 migrará los blobs a App Storage para cerrar I-01.</t>
   </si>
   <si>
     <t>I-02</t>
@@ -1450,7 +1450,7 @@
     <t>The punchlist is a core V1 construction-phase deliverable (Fase 5). Data persistence is a fundamental V1 infrastructure requirement.</t>
   </si>
   <si>
-    <t>EN: CSV column mapping wizard now auto-suggests mappings, supports manual override, and remembers the mapping per source (localStorage). | ES: El asistente de mapeo de columnas CSV ahora sugiere automáticamente, permite sobrescribir manualmente y recuerda el mapeo por fuente (localStorage).</t>
+    <t>EN: Punchlist persistence — PROJECT_PUNCHLIST is hydrated from disk on boot and saved on every change, so punchlist entries (incl. photo metadata) survive a server restart. Files: artifacts/api-server/src/routes/projects.ts. | ES: Persistencia del punchlist — PROJECT_PUNCHLIST se carga desde disco al iniciar y se guarda en cada cambio, sobreviviendo a un reinicio del servidor (incluye metadatos de fotos). Archivos: artifacts/api-server/src/routes/projects.ts.</t>
   </si>
   <si>
     <t>I-04</t>

--- a/attached_assets/reports/KONTi_Dashboard_Feedback_Consolidated_v4.xlsx
+++ b/attached_assets/reports/KONTi_Dashboard_Feedback_Consolidated_v4.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1199" uniqueCount="566">
   <si>
     <t>ID</t>
   </si>
@@ -1564,10 +1564,13 @@
     <t>Google Drive Integration</t>
   </si>
   <si>
-    <t>Audit snapshot (2026-04-29)</t>
+    <t>Audit snapshot (2026-04-30)</t>
   </si>
   <si>
     <t>gmena83/Arch-Firm-Hub @ main</t>
+  </si>
+  <si>
+    <t>Previous snapshot (2026-04-29)</t>
   </si>
   <si>
     <t>Field</t>
@@ -6097,7 +6100,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -6393,7 +6396,7 @@
         <v>27</v>
       </c>
       <c r="B38">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -6401,7 +6404,7 @@
         <v>117</v>
       </c>
       <c r="B39">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -6409,7 +6412,7 @@
         <v>37</v>
       </c>
       <c r="B40">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -6417,6 +6420,43 @@
         <v>109</v>
       </c>
       <c r="B41">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B44">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>117</v>
+      </c>
+      <c r="B45">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>109</v>
+      </c>
+      <c r="B47">
         <v>7</v>
       </c>
     </row>
@@ -6443,13 +6483,13 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="46" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B1" s="46" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C1" s="46" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6457,10 +6497,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6468,7 +6508,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>17</v>
@@ -6479,7 +6519,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>138</v>
@@ -6490,10 +6530,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6501,10 +6541,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6512,10 +6552,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6523,10 +6563,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6534,10 +6574,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6545,10 +6585,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6556,7 +6596,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>25</v>
@@ -6567,10 +6607,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6578,10 +6618,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6589,10 +6629,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6600,10 +6640,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6613,7 +6653,7 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="47" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
@@ -6623,10 +6663,10 @@
         <v>212</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6634,10 +6674,10 @@
         <v>21</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6645,10 +6685,10 @@
         <v>24</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6656,10 +6696,10 @@
         <v>54</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6667,10 +6707,10 @@
         <v>104</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6680,7 +6720,7 @@
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="47" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="5"/>
@@ -6690,7 +6730,7 @@
         <v>37</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C25" s="7"/>
     </row>
@@ -6699,7 +6739,7 @@
         <v>117</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C26" s="7"/>
     </row>
@@ -6708,7 +6748,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C27" s="7"/>
     </row>
@@ -6717,7 +6757,7 @@
         <v>501</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C28" s="7"/>
     </row>
@@ -6726,7 +6766,7 @@
         <v>109</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C29" s="7"/>
     </row>
@@ -6737,7 +6777,7 @@
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="47" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="5"/>
@@ -6747,7 +6787,7 @@
         <v>28</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C32" s="7"/>
     </row>
@@ -6756,7 +6796,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C33" s="7"/>
     </row>

--- a/attached_assets/reports/KONTi_Dashboard_Feedback_Consolidated_v4.xlsx
+++ b/attached_assets/reports/KONTi_Dashboard_Feedback_Consolidated_v4.xlsx
@@ -4761,7 +4761,7 @@
       </c>
       <c r="O57" s="11" t="inlineStr">
         <is>
-          <t>ContractorUploadModal (single + CSV modes) in artifacts/konti-dashboard/src/pages/team.tsx (~L69-115). NOTE: implemented despite being scoped V2.</t>
+          <t>EN: Already shipped despite V2 scope — ContractorUploadModal (single + CSV modes) on the Team Directory page. File: artifacts/konti-dashboard/src/pages/team.tsx (~L69-115). | ES: Ya implementado a pesar de estar en alcance V2 — ContractorUploadModal (modos individual + CSV) en la página de Directorio del Equipo. Archivo: artifacts/konti-dashboard/src/pages/team.tsx (~L69-115).</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="M17" s="16" t="inlineStr">
@@ -6427,6 +6427,11 @@
       <c r="N17" s="7" t="inlineStr">
         <is>
           <t>The V1 workflow does not include a contractor directory management module. Contractor tracking in V1 is limited to the project-level contractor monitoring report (Fase 5). A full contractor directory CRUD is a V2 HR/operations feature.</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>EN: Already shipped despite V2 scope — ContractorUploadModal (single + CSV modes) on the Team Directory page. File: artifacts/konti-dashboard/src/pages/team.tsx (~L69-115). | ES: Ya implementado a pesar de estar en alcance V2 — ContractorUploadModal (modos individual + CSV) en la página de Directorio del Equipo. Archivo: artifacts/konti-dashboard/src/pages/team.tsx (~L69-115).</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6792,7 +6797,7 @@
         </is>
       </c>
       <c r="B17" s="29" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -6812,7 +6817,7 @@
         </is>
       </c>
       <c r="B19" s="29" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -7011,7 +7016,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39">
@@ -7031,7 +7036,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
@@ -7059,7 +7064,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
@@ -7069,7 +7074,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46">
@@ -7079,7 +7084,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47">
@@ -7092,6 +7097,7 @@
         <v>7</v>
       </c>
     </row>
+    <row r="48"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>

--- a/attached_assets/reports/KONTi_Dashboard_Feedback_Consolidated_v4.xlsx
+++ b/attached_assets/reports/KONTi_Dashboard_Feedback_Consolidated_v4.xlsx
@@ -3849,7 +3849,7 @@
       </c>
       <c r="O42" s="11" t="inlineStr">
         <is>
-          <t>EN: Site photos in report — site-photos-gallery component is rendered on the project report and PHOTO_CATEGORY_OPTIONS is wired into the report's photos block so each photo carries a category label. File: artifacts/konti-dashboard/src/pages/project-report.tsx + components/site-photos-gallery.tsx. | ES: Fotos de obra en el reporte — el componente site-photos-gallery se muestra en el reporte del proyecto y PHOTO_CATEGORY_OPTIONS está conectado al bloque de fotos del reporte para que cada foto tenga etiqueta de categoría. Archivo: artifacts/konti-dashboard/src/pages/project-report.tsx + components/site-photos-gallery.tsx.</t>
+          <t>EN: Done in #105 — Site photos in the project report: site-photos-gallery component is rendered on the project report and PHOTO_CATEGORY_OPTIONS is wired into the report's photos block so each photo carries a category label. File: artifacts/konti-dashboard/src/pages/project-report.tsx + artifacts/konti-dashboard/src/components/site-photos-gallery.tsx. | ES: Hecho en #105 — Fotos de obra en el reporte del proyecto: el componente site-photos-gallery se muestra en el reporte del proyecto y PHOTO_CATEGORY_OPTIONS está conectado al bloque de fotos del reporte para que cada foto tenga etiqueta de categoría. Archivo: artifacts/konti-dashboard/src/pages/project-report.tsx + artifacts/konti-dashboard/src/components/site-photos-gallery.tsx.</t>
         </is>
       </c>
     </row>
